--- a/results_task_2/deepseek/2_Y_N_TG_6_oil50.xlsx
+++ b/results_task_2/deepseek/2_Y_N_TG_6_oil50.xlsx
@@ -546,7 +546,7 @@
         <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -608,7 +608,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -670,7 +670,7 @@
         <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
